--- a/Deliverables/Interface_Board/BOM/Interface_Board_BOM Quantity(500).xlsx
+++ b/Deliverables/Interface_Board/BOM/Interface_Board_BOM Quantity(500).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ChristianRaun-EthercatDesign\Deliverables\Interface_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18AF3744-408B-4999-A382-2D8A816A841D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B33E60E-95C2-4257-A4BA-8AE873376A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="268">
   <si>
     <t>Component list</t>
   </si>
@@ -765,9 +765,6 @@
     <t>C86471</t>
   </si>
   <si>
-    <t>Need Quote from Custom Supplier</t>
-  </si>
-  <si>
     <t xml:space="preserve">Total Component Cost </t>
   </si>
   <si>
@@ -835,6 +832,12 @@
   </si>
   <si>
     <t>Test Point</t>
+  </si>
+  <si>
+    <t>Custom Supplier</t>
+  </si>
+  <si>
+    <t>Karen Quotes</t>
   </si>
 </sst>
 </file>
@@ -1383,7 +1386,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1627,9 +1630,6 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="19" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="19" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1683,51 +1683,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="19" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1760,7 +1715,49 @@
     <xf numFmtId="0" fontId="22" fillId="2" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2121,7 +2118,7 @@
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18" customWidth="1"/>
@@ -2139,20 +2136,20 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="112"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="119"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
-      <c r="C2" s="91"/>
+      <c r="C2" s="90"/>
       <c r="D2" s="10" t="s">
         <v>0</v>
       </c>
@@ -2177,7 +2174,7 @@
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
-      <c r="C3" s="92"/>
+      <c r="C3" s="91"/>
       <c r="D3" s="12" t="s">
         <v>1</v>
       </c>
@@ -2197,12 +2194,12 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="113"/>
+      <c r="S3" s="120"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
-      <c r="C4" s="92"/>
+      <c r="C4" s="91"/>
       <c r="D4" s="12" t="s">
         <v>2</v>
       </c>
@@ -2222,12 +2219,12 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="114"/>
+      <c r="S4" s="121"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
-      <c r="C5" s="92"/>
+      <c r="C5" s="91"/>
       <c r="D5" s="12" t="s">
         <v>3</v>
       </c>
@@ -2247,12 +2244,12 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="114"/>
+      <c r="S5" s="121"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
-      <c r="C6" s="93"/>
+      <c r="C6" s="92"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="16"/>
@@ -2268,12 +2265,12 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="114"/>
+      <c r="S6" s="121"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
-      <c r="C7" s="94"/>
+      <c r="C7" s="93"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
@@ -2289,12 +2286,12 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="114"/>
+      <c r="S7" s="121"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="25"/>
-      <c r="C8" s="95"/>
+      <c r="C8" s="94"/>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
       <c r="F8" s="27"/>
@@ -2310,7 +2307,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="114"/>
+      <c r="S8" s="121"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2318,7 +2315,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D9" s="28" t="s">
         <v>10</v>
@@ -2351,7 +2348,7 @@
         <v>191</v>
       </c>
       <c r="N9" s="28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O9" s="28" t="s">
         <v>192</v>
@@ -2375,8 +2372,8 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="108" t="s">
-        <v>249</v>
+      <c r="C10" s="129" t="s">
+        <v>248</v>
       </c>
       <c r="D10" s="41" t="s">
         <v>11</v>
@@ -2415,7 +2412,7 @@
       <c r="O10" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="P10" s="105">
+      <c r="P10" s="104">
         <v>2.3199999999999998E-2</v>
       </c>
       <c r="Q10" s="51">
@@ -2431,7 +2428,7 @@
         <f t="shared" ref="B11:B49" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="109"/>
+      <c r="C11" s="130"/>
       <c r="D11" s="45" t="s">
         <v>12</v>
       </c>
@@ -2441,7 +2438,7 @@
       <c r="F11" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="G11" s="102" t="s">
+      <c r="G11" s="101" t="s">
         <v>120</v>
       </c>
       <c r="H11" s="45" t="s">
@@ -2469,7 +2466,7 @@
       <c r="O11" s="64" t="s">
         <v>197</v>
       </c>
-      <c r="P11" s="90">
+      <c r="P11" s="89">
         <v>1.4200000000000001E-2</v>
       </c>
       <c r="Q11" s="54">
@@ -2485,7 +2482,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="109"/>
+      <c r="C12" s="130"/>
       <c r="D12" s="41" t="s">
         <v>13</v>
       </c>
@@ -2523,7 +2520,7 @@
       <c r="O12" s="71" t="s">
         <v>197</v>
       </c>
-      <c r="P12" s="105">
+      <c r="P12" s="104">
         <v>7.3599999999999999E-2</v>
       </c>
       <c r="Q12" s="51">
@@ -2539,7 +2536,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="109"/>
+      <c r="C13" s="130"/>
       <c r="D13" s="45" t="s">
         <v>14</v>
       </c>
@@ -2574,18 +2571,18 @@
       <c r="N13" s="47">
         <v>1520</v>
       </c>
-      <c r="O13" s="72" t="s">
-        <v>197</v>
-      </c>
-      <c r="P13" s="90">
-        <v>0.1555</v>
+      <c r="O13" s="75" t="s">
+        <v>266</v>
+      </c>
+      <c r="P13" s="89">
+        <v>0.1</v>
       </c>
       <c r="Q13" s="54">
         <f t="shared" si="2"/>
-        <v>236.35999999999999</v>
-      </c>
-      <c r="R13" s="129" t="s">
-        <v>204</v>
+        <v>152</v>
+      </c>
+      <c r="R13" s="114" t="s">
+        <v>267</v>
       </c>
       <c r="S13" s="49"/>
     </row>
@@ -2595,7 +2592,7 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="109"/>
+      <c r="C14" s="130"/>
       <c r="D14" s="41" t="s">
         <v>15</v>
       </c>
@@ -2633,7 +2630,7 @@
       <c r="O14" s="73" t="s">
         <v>197</v>
       </c>
-      <c r="P14" s="105">
+      <c r="P14" s="104">
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="Q14" s="51">
@@ -2649,7 +2646,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="109"/>
+      <c r="C15" s="130"/>
       <c r="D15" s="45" t="s">
         <v>16</v>
       </c>
@@ -2659,7 +2656,7 @@
       <c r="F15" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="G15" s="102" t="s">
+      <c r="G15" s="101" t="s">
         <v>122</v>
       </c>
       <c r="H15" s="45" t="s">
@@ -2687,7 +2684,7 @@
       <c r="O15" s="74" t="s">
         <v>197</v>
       </c>
-      <c r="P15" s="90">
+      <c r="P15" s="89">
         <v>2.5999999999999999E-3</v>
       </c>
       <c r="Q15" s="54">
@@ -2703,7 +2700,7 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="109"/>
+      <c r="C16" s="130"/>
       <c r="D16" s="41" t="s">
         <v>17</v>
       </c>
@@ -2713,7 +2710,7 @@
       <c r="F16" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="G16" s="103" t="s">
+      <c r="G16" s="102" t="s">
         <v>123</v>
       </c>
       <c r="H16" s="65" t="s">
@@ -2741,7 +2738,7 @@
       <c r="O16" s="71" t="s">
         <v>197</v>
       </c>
-      <c r="P16" s="105">
+      <c r="P16" s="104">
         <v>4.7999999999999996E-3</v>
       </c>
       <c r="Q16" s="51">
@@ -2757,7 +2754,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="109"/>
+      <c r="C17" s="130"/>
       <c r="D17" s="45" t="s">
         <v>18</v>
       </c>
@@ -2795,7 +2792,7 @@
       <c r="O17" s="64" t="s">
         <v>197</v>
       </c>
-      <c r="P17" s="90">
+      <c r="P17" s="89">
         <v>9.4999999999999998E-3</v>
       </c>
       <c r="Q17" s="54">
@@ -2811,7 +2808,7 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="109"/>
+      <c r="C18" s="130"/>
       <c r="D18" s="41" t="s">
         <v>19</v>
       </c>
@@ -2849,7 +2846,7 @@
       <c r="O18" s="73" t="s">
         <v>197</v>
       </c>
-      <c r="P18" s="105">
+      <c r="P18" s="104">
         <v>4.7999999999999996E-3</v>
       </c>
       <c r="Q18" s="51">
@@ -2865,7 +2862,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="109"/>
+      <c r="C19" s="130"/>
       <c r="D19" s="45" t="s">
         <v>20</v>
       </c>
@@ -2903,7 +2900,7 @@
       <c r="O19" s="75" t="s">
         <v>197</v>
       </c>
-      <c r="P19" s="90">
+      <c r="P19" s="89">
         <v>1.6400000000000001E-2</v>
       </c>
       <c r="Q19" s="54">
@@ -2919,7 +2916,7 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="110"/>
+      <c r="C20" s="131"/>
       <c r="D20" s="41" t="s">
         <v>21</v>
       </c>
@@ -2957,14 +2954,14 @@
       <c r="O20" s="73" t="s">
         <v>197</v>
       </c>
-      <c r="P20" s="105">
+      <c r="P20" s="104">
         <v>7.7200000000000005E-2</v>
       </c>
       <c r="Q20" s="51">
         <f t="shared" si="2"/>
         <v>78.744</v>
       </c>
-      <c r="R20" s="130" t="s">
+      <c r="R20" s="115" t="s">
         <v>204</v>
       </c>
       <c r="S20" s="57"/>
@@ -2975,8 +2972,8 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="109" t="s">
-        <v>250</v>
+      <c r="C21" s="130" t="s">
+        <v>249</v>
       </c>
       <c r="D21" s="45" t="s">
         <v>22</v>
@@ -3015,7 +3012,7 @@
       <c r="O21" s="75" t="s">
         <v>197</v>
       </c>
-      <c r="P21" s="90">
+      <c r="P21" s="89">
         <v>0.26669999999999999</v>
       </c>
       <c r="Q21" s="54">
@@ -3031,7 +3028,7 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="109"/>
+      <c r="C22" s="130"/>
       <c r="D22" s="41" t="s">
         <v>23</v>
       </c>
@@ -3069,14 +3066,14 @@
       <c r="O22" s="67" t="s">
         <v>197</v>
       </c>
-      <c r="P22" s="105">
+      <c r="P22" s="104">
         <v>2.6100000000000002E-2</v>
       </c>
       <c r="Q22" s="51">
         <f t="shared" si="2"/>
         <v>13.572000000000001</v>
       </c>
-      <c r="R22" s="130"/>
+      <c r="R22" s="115"/>
       <c r="S22" s="57"/>
     </row>
     <row r="23" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3085,7 +3082,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="109"/>
+      <c r="C23" s="130"/>
       <c r="D23" s="45" t="s">
         <v>24</v>
       </c>
@@ -3123,7 +3120,7 @@
       <c r="O23" s="75" t="s">
         <v>197</v>
       </c>
-      <c r="P23" s="90">
+      <c r="P23" s="89">
         <v>1.78E-2</v>
       </c>
       <c r="Q23" s="54">
@@ -3139,7 +3136,7 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="109"/>
+      <c r="C24" s="130"/>
       <c r="D24" s="41" t="s">
         <v>25</v>
       </c>
@@ -3177,7 +3174,7 @@
       <c r="O24" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="P24" s="105">
+      <c r="P24" s="104">
         <v>5.6599999999999998E-2</v>
       </c>
       <c r="Q24" s="51">
@@ -3193,16 +3190,16 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="108" t="s">
-        <v>251</v>
+      <c r="C25" s="129" t="s">
+        <v>250</v>
       </c>
       <c r="D25" s="45" t="s">
         <v>26</v>
       </c>
       <c r="E25" s="45" t="s">
-        <v>264</v>
-      </c>
-      <c r="F25" s="99" t="s">
+        <v>263</v>
+      </c>
+      <c r="F25" s="98" t="s">
         <v>201</v>
       </c>
       <c r="G25" s="45" t="s">
@@ -3233,7 +3230,7 @@
       <c r="O25" s="75" t="s">
         <v>239</v>
       </c>
-      <c r="P25" s="90">
+      <c r="P25" s="89">
         <v>0.32579999999999998</v>
       </c>
       <c r="Q25" s="54">
@@ -3249,14 +3246,14 @@
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="109"/>
+      <c r="C26" s="130"/>
       <c r="D26" s="41" t="s">
         <v>27</v>
       </c>
       <c r="E26" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="F26" s="100" t="s">
+      <c r="F26" s="99" t="s">
         <v>201</v>
       </c>
       <c r="G26" s="41" t="s">
@@ -3287,7 +3284,7 @@
       <c r="O26" s="63" t="s">
         <v>197</v>
       </c>
-      <c r="P26" s="105">
+      <c r="P26" s="104">
         <v>1.2641</v>
       </c>
       <c r="Q26" s="51">
@@ -3303,14 +3300,14 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="110"/>
+      <c r="C27" s="131"/>
       <c r="D27" s="45" t="s">
         <v>28</v>
       </c>
       <c r="E27" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="F27" s="99" t="s">
+      <c r="F27" s="98" t="s">
         <v>201</v>
       </c>
       <c r="G27" s="45" t="s">
@@ -3341,7 +3338,7 @@
       <c r="O27" s="55" t="s">
         <v>239</v>
       </c>
-      <c r="P27" s="90">
+      <c r="P27" s="89">
         <v>0.16800000000000001</v>
       </c>
       <c r="Q27" s="54">
@@ -3357,8 +3354,8 @@
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="108" t="s">
-        <v>252</v>
+      <c r="C28" s="129" t="s">
+        <v>251</v>
       </c>
       <c r="D28" s="41" t="s">
         <v>29</v>
@@ -3366,7 +3363,7 @@
       <c r="E28" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="F28" s="100" t="s">
+      <c r="F28" s="99" t="s">
         <v>201</v>
       </c>
       <c r="G28" s="41" t="s">
@@ -3397,7 +3394,7 @@
       <c r="O28" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="P28" s="105">
+      <c r="P28" s="104">
         <v>3.8600000000000002E-2</v>
       </c>
       <c r="Q28" s="51">
@@ -3407,13 +3404,13 @@
       <c r="R28" s="41"/>
       <c r="S28" s="57"/>
     </row>
-    <row r="29" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="36">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="131"/>
       <c r="D29" s="45" t="s">
         <v>30</v>
       </c>
@@ -3426,7 +3423,9 @@
       <c r="G29" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="H29" s="45"/>
+      <c r="H29" s="53" t="s">
+        <v>211</v>
+      </c>
       <c r="I29" s="48" t="s">
         <v>151</v>
       </c>
@@ -3443,15 +3442,21 @@
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N29" s="47"/>
-      <c r="O29" s="45"/>
-      <c r="P29" s="90"/>
+      <c r="N29" s="47">
+        <v>505</v>
+      </c>
+      <c r="O29" s="75" t="s">
+        <v>266</v>
+      </c>
+      <c r="P29" s="89">
+        <v>0.73</v>
+      </c>
       <c r="Q29" s="54">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R29" s="129" t="s">
-        <v>243</v>
+        <v>368.65</v>
+      </c>
+      <c r="R29" s="114" t="s">
+        <v>267</v>
       </c>
       <c r="S29" s="49"/>
     </row>
@@ -3461,8 +3466,8 @@
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="108" t="s">
-        <v>251</v>
+      <c r="C30" s="129" t="s">
+        <v>250</v>
       </c>
       <c r="D30" s="41" t="s">
         <v>31</v>
@@ -3501,7 +3506,7 @@
       <c r="O30" s="77" t="s">
         <v>197</v>
       </c>
-      <c r="P30" s="105">
+      <c r="P30" s="104">
         <v>2.47E-2</v>
       </c>
       <c r="Q30" s="51">
@@ -3517,7 +3522,7 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="109"/>
+      <c r="C31" s="130"/>
       <c r="D31" s="45" t="s">
         <v>32</v>
       </c>
@@ -3555,15 +3560,15 @@
       <c r="O31" s="78" t="s">
         <v>197</v>
       </c>
-      <c r="P31" s="90">
+      <c r="P31" s="89">
         <v>0.20269999999999999</v>
       </c>
       <c r="Q31" s="54">
         <f t="shared" si="2"/>
         <v>203.71349999999998</v>
       </c>
-      <c r="R31" s="131" t="s">
-        <v>257</v>
+      <c r="R31" s="116" t="s">
+        <v>256</v>
       </c>
       <c r="S31" s="49"/>
     </row>
@@ -3573,8 +3578,8 @@
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="98" t="s">
-        <v>266</v>
+      <c r="C32" s="97" t="s">
+        <v>265</v>
       </c>
       <c r="D32" s="41" t="s">
         <v>33</v>
@@ -3619,7 +3624,7 @@
       <c r="Q32" s="56" t="s">
         <v>202</v>
       </c>
-      <c r="R32" s="132" t="s">
+      <c r="R32" s="117" t="s">
         <v>231</v>
       </c>
       <c r="S32" s="57"/>
@@ -3630,8 +3635,8 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="97" t="s">
-        <v>253</v>
+      <c r="C33" s="96" t="s">
+        <v>252</v>
       </c>
       <c r="D33" s="45" t="s">
         <v>34</v>
@@ -3642,7 +3647,7 @@
       <c r="F33" s="46" t="s">
         <v>201</v>
       </c>
-      <c r="G33" s="104" t="s">
+      <c r="G33" s="103" t="s">
         <v>108</v>
       </c>
       <c r="H33" s="53" t="s">
@@ -3670,7 +3675,7 @@
       <c r="O33" s="79" t="s">
         <v>197</v>
       </c>
-      <c r="P33" s="90">
+      <c r="P33" s="89">
         <v>0.56630000000000003</v>
       </c>
       <c r="Q33" s="54">
@@ -3686,8 +3691,8 @@
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="98" t="s">
-        <v>254</v>
+      <c r="C34" s="97" t="s">
+        <v>253</v>
       </c>
       <c r="D34" s="41" t="s">
         <v>35</v>
@@ -3726,7 +3731,7 @@
       <c r="O34" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="P34" s="105">
+      <c r="P34" s="104">
         <v>4.4699999999999997E-2</v>
       </c>
       <c r="Q34" s="51">
@@ -3742,8 +3747,8 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="108" t="s">
-        <v>255</v>
+      <c r="C35" s="129" t="s">
+        <v>254</v>
       </c>
       <c r="D35" s="45" t="s">
         <v>36</v>
@@ -3782,7 +3787,7 @@
       <c r="O35" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="P35" s="90">
+      <c r="P35" s="89">
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="Q35" s="54">
@@ -3798,7 +3803,7 @@
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="109"/>
+      <c r="C36" s="130"/>
       <c r="D36" s="41" t="s">
         <v>37</v>
       </c>
@@ -3808,17 +3813,17 @@
       <c r="F36" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G36" s="103" t="s">
+      <c r="G36" s="102" t="s">
         <v>130</v>
       </c>
       <c r="H36" s="41" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I36" s="43" t="s">
         <v>153</v>
       </c>
       <c r="J36" s="41" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K36" s="41" t="s">
         <v>178</v>
@@ -3836,7 +3841,7 @@
       <c r="O36" s="63" t="s">
         <v>197</v>
       </c>
-      <c r="P36" s="105">
+      <c r="P36" s="104">
         <v>1.4E-3</v>
       </c>
       <c r="Q36" s="51">
@@ -3852,7 +3857,7 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="109"/>
+      <c r="C37" s="130"/>
       <c r="D37" s="45" t="s">
         <v>38</v>
       </c>
@@ -3862,7 +3867,7 @@
       <c r="F37" s="46" t="s">
         <v>111</v>
       </c>
-      <c r="G37" s="102" t="s">
+      <c r="G37" s="101" t="s">
         <v>131</v>
       </c>
       <c r="H37" s="59" t="s">
@@ -3890,7 +3895,7 @@
       <c r="O37" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="P37" s="90">
+      <c r="P37" s="89">
         <v>9.8699999999999996E-2</v>
       </c>
       <c r="Q37" s="54">
@@ -3906,7 +3911,7 @@
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="109"/>
+      <c r="C38" s="130"/>
       <c r="D38" s="41" t="s">
         <v>39</v>
       </c>
@@ -3916,17 +3921,17 @@
       <c r="F38" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="G38" s="103" t="s">
-        <v>261</v>
+      <c r="G38" s="102" t="s">
+        <v>260</v>
       </c>
       <c r="H38" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="I38" s="43" t="s">
         <v>258</v>
       </c>
-      <c r="I38" s="43" t="s">
+      <c r="J38" s="41" t="s">
         <v>259</v>
-      </c>
-      <c r="J38" s="41" t="s">
-        <v>260</v>
       </c>
       <c r="K38" s="41" t="s">
         <v>180</v>
@@ -3944,7 +3949,7 @@
       <c r="O38" s="63" t="s">
         <v>197</v>
       </c>
-      <c r="P38" s="105">
+      <c r="P38" s="104">
         <v>3.2399999999999998E-2</v>
       </c>
       <c r="Q38" s="51">
@@ -3960,7 +3965,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="109"/>
+      <c r="C39" s="130"/>
       <c r="D39" s="45" t="s">
         <v>40</v>
       </c>
@@ -3998,7 +4003,7 @@
       <c r="O39" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="P39" s="90">
+      <c r="P39" s="89">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q39" s="54">
@@ -4014,7 +4019,7 @@
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="109"/>
+      <c r="C40" s="130"/>
       <c r="D40" s="41" t="s">
         <v>41</v>
       </c>
@@ -4052,7 +4057,7 @@
       <c r="O40" s="81" t="s">
         <v>197</v>
       </c>
-      <c r="P40" s="105">
+      <c r="P40" s="104">
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="Q40" s="51">
@@ -4068,7 +4073,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="109"/>
+      <c r="C41" s="130"/>
       <c r="D41" s="45" t="s">
         <v>42</v>
       </c>
@@ -4106,7 +4111,7 @@
       <c r="O41" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="P41" s="90">
+      <c r="P41" s="89">
         <v>1E-3</v>
       </c>
       <c r="Q41" s="54">
@@ -4122,7 +4127,7 @@
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="109"/>
+      <c r="C42" s="130"/>
       <c r="D42" s="41" t="s">
         <v>43</v>
       </c>
@@ -4160,7 +4165,7 @@
       <c r="O42" s="82" t="s">
         <v>197</v>
       </c>
-      <c r="P42" s="105">
+      <c r="P42" s="104">
         <v>2.46E-2</v>
       </c>
       <c r="Q42" s="51">
@@ -4176,7 +4181,7 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="109"/>
+      <c r="C43" s="130"/>
       <c r="D43" s="45" t="s">
         <v>44</v>
       </c>
@@ -4214,7 +4219,7 @@
       <c r="O43" s="83" t="s">
         <v>197</v>
       </c>
-      <c r="P43" s="90">
+      <c r="P43" s="89">
         <v>3.3999999999999998E-3</v>
       </c>
       <c r="Q43" s="54">
@@ -4230,7 +4235,7 @@
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="109"/>
+      <c r="C44" s="130"/>
       <c r="D44" s="41" t="s">
         <v>45</v>
       </c>
@@ -4268,7 +4273,7 @@
       <c r="O44" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="P44" s="105">
+      <c r="P44" s="104">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q44" s="51">
@@ -4284,7 +4289,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="110"/>
+      <c r="C45" s="131"/>
       <c r="D45" s="45" t="s">
         <v>46</v>
       </c>
@@ -4322,7 +4327,7 @@
       <c r="O45" s="83" t="s">
         <v>197</v>
       </c>
-      <c r="P45" s="90">
+      <c r="P45" s="89">
         <v>1.12E-2</v>
       </c>
       <c r="Q45" s="54">
@@ -4338,7 +4343,7 @@
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="98" t="s">
+      <c r="C46" s="97" t="s">
         <v>114</v>
       </c>
       <c r="D46" s="41" t="s">
@@ -4378,13 +4383,13 @@
       <c r="O46" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="P46" s="106" t="s">
+      <c r="P46" s="105" t="s">
         <v>202</v>
       </c>
       <c r="Q46" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="R46" s="132" t="s">
+      <c r="R46" s="117" t="s">
         <v>231</v>
       </c>
       <c r="S46" s="60" t="s">
@@ -4397,8 +4402,8 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="109" t="s">
-        <v>256</v>
+      <c r="C47" s="130" t="s">
+        <v>255</v>
       </c>
       <c r="D47" s="45" t="s">
         <v>48</v>
@@ -4431,15 +4436,21 @@
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N47" s="45"/>
-      <c r="O47" s="45"/>
-      <c r="P47" s="90"/>
+      <c r="N47" s="45">
+        <v>505</v>
+      </c>
+      <c r="O47" s="75" t="s">
+        <v>266</v>
+      </c>
+      <c r="P47" s="89">
+        <v>2.96</v>
+      </c>
       <c r="Q47" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R47" s="129" t="s">
-        <v>243</v>
+        <v>1494.8</v>
+      </c>
+      <c r="R47" s="114" t="s">
+        <v>267</v>
       </c>
       <c r="S47" s="49"/>
     </row>
@@ -4449,14 +4460,14 @@
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
-      <c r="C48" s="109"/>
+      <c r="C48" s="130"/>
       <c r="D48" s="41" t="s">
         <v>49</v>
       </c>
       <c r="E48" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="F48" s="101" t="s">
+      <c r="F48" s="100" t="s">
         <v>232</v>
       </c>
       <c r="G48" s="41" t="s">
@@ -4487,7 +4498,7 @@
       <c r="O48" s="84" t="s">
         <v>197</v>
       </c>
-      <c r="P48" s="105">
+      <c r="P48" s="104">
         <v>3.1503999999999999</v>
       </c>
       <c r="Q48" s="51">
@@ -4503,7 +4514,7 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="131"/>
       <c r="D49" s="45" t="s">
         <v>50</v>
       </c>
@@ -4511,7 +4522,7 @@
         <v>90</v>
       </c>
       <c r="F49" s="46" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G49" s="61" t="s">
         <v>117</v>
@@ -4522,7 +4533,9 @@
       <c r="I49" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="J49" s="45"/>
+      <c r="J49" s="53" t="s">
+        <v>202</v>
+      </c>
       <c r="K49" s="53" t="s">
         <v>202</v>
       </c>
@@ -4536,23 +4549,25 @@
       <c r="N49" s="88">
         <v>505</v>
       </c>
-      <c r="O49" s="89" t="s">
-        <v>197</v>
-      </c>
-      <c r="P49" s="90"/>
-      <c r="Q49" s="107">
+      <c r="O49" s="75" t="s">
+        <v>266</v>
+      </c>
+      <c r="P49" s="89">
+        <v>0.1</v>
+      </c>
+      <c r="Q49" s="106">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R49" s="133" t="s">
-        <v>243</v>
+        <v>50.5</v>
+      </c>
+      <c r="R49" s="114" t="s">
+        <v>267</v>
       </c>
       <c r="S49" s="49"/>
     </row>
     <row r="50" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="31"/>
-      <c r="C50" s="96"/>
+      <c r="C50" s="95"/>
       <c r="D50" s="32" t="s">
         <v>5</v>
       </c>
@@ -4564,45 +4579,45 @@
       <c r="J50" s="34"/>
       <c r="K50" s="35"/>
       <c r="L50" s="35"/>
-      <c r="M50" s="122"/>
-      <c r="N50" s="117" t="s">
-        <v>244</v>
-      </c>
-      <c r="O50" s="118"/>
-      <c r="P50" s="118"/>
+      <c r="M50" s="107"/>
+      <c r="N50" s="122" t="s">
+        <v>243</v>
+      </c>
+      <c r="O50" s="123"/>
+      <c r="P50" s="123"/>
       <c r="Q50" s="85">
         <f>SUM(Q10:Q49)</f>
-        <v>4446.1555000000008</v>
-      </c>
-      <c r="R50" s="120"/>
-      <c r="S50" s="115"/>
+        <v>6275.7455000000009</v>
+      </c>
+      <c r="R50" s="125"/>
+      <c r="S50" s="126"/>
     </row>
     <row r="51" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
-      <c r="B51" s="123"/>
-      <c r="C51" s="124"/>
+      <c r="B51" s="108"/>
+      <c r="C51" s="109"/>
       <c r="D51" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="E51" s="125"/>
-      <c r="F51" s="126"/>
-      <c r="G51" s="127"/>
-      <c r="H51" s="127"/>
-      <c r="I51" s="126"/>
-      <c r="J51" s="126"/>
-      <c r="K51" s="127"/>
-      <c r="L51" s="127"/>
-      <c r="M51" s="128"/>
-      <c r="N51" s="117" t="s">
-        <v>246</v>
-      </c>
-      <c r="O51" s="118"/>
-      <c r="P51" s="119"/>
+      <c r="E51" s="110"/>
+      <c r="F51" s="111"/>
+      <c r="G51" s="112"/>
+      <c r="H51" s="112"/>
+      <c r="I51" s="111"/>
+      <c r="J51" s="111"/>
+      <c r="K51" s="112"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="113"/>
+      <c r="N51" s="122" t="s">
+        <v>245</v>
+      </c>
+      <c r="O51" s="123"/>
+      <c r="P51" s="124"/>
       <c r="Q51" s="87">
         <v>67.599999999999994</v>
       </c>
-      <c r="R51" s="121"/>
-      <c r="S51" s="116"/>
+      <c r="R51" s="127"/>
+      <c r="S51" s="128"/>
     </row>
     <row r="52" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
@@ -4616,24 +4631,18 @@
       <c r="K52" s="24"/>
       <c r="L52" s="24"/>
       <c r="M52" s="24"/>
-      <c r="N52" s="117" t="s">
-        <v>245</v>
-      </c>
-      <c r="O52" s="118"/>
-      <c r="P52" s="118"/>
+      <c r="N52" s="122" t="s">
+        <v>244</v>
+      </c>
+      <c r="O52" s="123"/>
+      <c r="P52" s="123"/>
       <c r="Q52" s="86">
         <f>Q50/500</f>
-        <v>8.8923110000000012</v>
+        <v>12.551491000000002</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R50:S51"/>
     <mergeCell ref="C35:C45"/>
     <mergeCell ref="C47:C49"/>
     <mergeCell ref="C10:C20"/>
@@ -4641,9 +4650,15 @@
     <mergeCell ref="C25:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R50:S51"/>
   </mergeCells>
   <conditionalFormatting sqref="O14">
-    <cfRule type="dataBar" priority="11">
+    <cfRule type="dataBar" priority="15">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4657,7 +4672,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O18">
-    <cfRule type="dataBar" priority="9">
+    <cfRule type="dataBar" priority="13">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4671,7 +4686,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O19">
-    <cfRule type="dataBar" priority="8">
+    <cfRule type="dataBar" priority="12">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4685,7 +4700,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O20">
-    <cfRule type="dataBar" priority="6">
+    <cfRule type="dataBar" priority="10">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4699,7 +4714,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O21">
-    <cfRule type="dataBar" priority="5">
+    <cfRule type="dataBar" priority="9">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4713,7 +4728,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O23">
-    <cfRule type="dataBar" priority="4">
+    <cfRule type="dataBar" priority="8">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4727,7 +4742,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O33">
-    <cfRule type="dataBar" priority="3">
+    <cfRule type="dataBar" priority="7">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4741,7 +4756,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O40">
-    <cfRule type="dataBar" priority="2">
+    <cfRule type="dataBar" priority="6">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4755,7 +4770,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O25">
-    <cfRule type="dataBar" priority="1">
+    <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4768,47 +4783,101 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="O29">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C425534F-2132-4E3E-9E27-4731DA9BFCD1}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O47">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{66F3904F-387C-4CAD-BEC6-08FB3198833C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O49">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0840C77E-1C20-4E52-9B84-C937166616D1}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O13">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{A36A295E-890B-44B2-8B87-7FA091974DAC}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1" xr:uid="{1B6B54E8-03CF-40A3-B32B-4151F2017DDB}"/>
     <hyperlink ref="O12" r:id="rId2" xr:uid="{A6AF3D12-A2B7-406C-99DE-4A2B14492EBF}"/>
-    <hyperlink ref="O13" r:id="rId3" xr:uid="{32CD3457-BA26-4F92-A976-07BE24A579BC}"/>
-    <hyperlink ref="O14" r:id="rId4" xr:uid="{42D3E95E-4A54-4681-8DD2-B405F8766920}"/>
-    <hyperlink ref="O15" r:id="rId5" xr:uid="{84858A17-343C-4382-89D9-8E88B2679CF6}"/>
-    <hyperlink ref="O16" r:id="rId6" xr:uid="{1D42C161-9348-4E50-8829-4A2AB74BE576}"/>
-    <hyperlink ref="O17" r:id="rId7" xr:uid="{77D8AFD1-CA93-40B0-9AB1-01AFA20E8CBF}"/>
-    <hyperlink ref="O18" r:id="rId8" xr:uid="{022A5E50-C635-4680-A1A7-9FD01AB2DCB9}"/>
-    <hyperlink ref="O19" r:id="rId9" xr:uid="{AF8FC433-8557-4930-9F93-B0BDC0D93633}"/>
-    <hyperlink ref="O20" r:id="rId10" xr:uid="{5D8D396A-4B9E-4433-AC86-359BF9C2E836}"/>
-    <hyperlink ref="O21" r:id="rId11" xr:uid="{24AD814A-F8AC-44A9-A96B-512C2D4D4A9E}"/>
-    <hyperlink ref="O23" r:id="rId12" xr:uid="{05628E33-6E5F-4008-A818-B731C118EC5E}"/>
-    <hyperlink ref="O24" r:id="rId13" xr:uid="{88128F9D-7EFF-4D52-87D7-9ABB22B3FE7D}"/>
-    <hyperlink ref="O33" r:id="rId14" xr:uid="{991349B4-FA5F-46BE-92E5-E5228174FB13}"/>
-    <hyperlink ref="O34" r:id="rId15" xr:uid="{D20CC96C-F0B2-4507-9A17-C43EF77BFED5}"/>
-    <hyperlink ref="O35" r:id="rId16" xr:uid="{C31D8FA7-31D2-4F7A-AAF2-A35193C83DEB}"/>
-    <hyperlink ref="O37" r:id="rId17" xr:uid="{108D1389-3DE9-4341-B4CD-5862FD176D0E}"/>
-    <hyperlink ref="O39" r:id="rId18" xr:uid="{078D3269-7E5E-40E1-AA3C-DA4DE0F331AB}"/>
-    <hyperlink ref="O40" r:id="rId19" xr:uid="{FB1093E0-651D-429A-8ECF-27D6532353DA}"/>
-    <hyperlink ref="O41" r:id="rId20" xr:uid="{71099F03-EFD3-4608-B59C-4F7AE5EF6DBF}"/>
-    <hyperlink ref="O42" r:id="rId21" xr:uid="{237BD033-D3F3-4E5B-9D55-F222CBCDA51A}"/>
-    <hyperlink ref="O43" r:id="rId22" xr:uid="{ABA061C0-3178-4EEE-AC9E-00F3074CCA83}"/>
-    <hyperlink ref="O44" r:id="rId23" xr:uid="{E3D102C8-0F26-49E0-9DD2-8086B665C1A9}"/>
-    <hyperlink ref="O45" r:id="rId24" xr:uid="{5F351CAB-DED2-4547-A277-A2BD52DD8FA7}"/>
-    <hyperlink ref="O48" r:id="rId25" xr:uid="{2E5DC74F-6A03-4F11-A724-94718B7221E7}"/>
-    <hyperlink ref="O11" r:id="rId26" xr:uid="{9E8A17B7-5D2F-4C74-B22B-A47931EE4D28}"/>
-    <hyperlink ref="O22" r:id="rId27" xr:uid="{0D6B720F-74DB-4906-B7E4-12F9EBBB2CD7}"/>
-    <hyperlink ref="O26" r:id="rId28" xr:uid="{E6C2E888-5DFE-4518-B9DA-59675AD20B1F}"/>
-    <hyperlink ref="O27" r:id="rId29" xr:uid="{7F9E98A4-2FC1-4E25-8EFE-AC9AD2673293}"/>
-    <hyperlink ref="O28" r:id="rId30" xr:uid="{7B2A4AC0-A421-4755-B302-91033C8526E7}"/>
-    <hyperlink ref="O30" r:id="rId31" xr:uid="{1566147B-6D46-410E-9332-C2A8C56F7EF8}"/>
-    <hyperlink ref="O31" r:id="rId32" xr:uid="{B2A3A2E4-A598-499D-8F57-43F54F143C2A}"/>
-    <hyperlink ref="O49" r:id="rId33" xr:uid="{B2F857CA-150F-4BAF-9CDD-A3F0783FADD5}"/>
-    <hyperlink ref="O25" r:id="rId34" xr:uid="{D6A67807-A726-4FC2-AE6E-F7CFE64FA5E5}"/>
-    <hyperlink ref="O38" r:id="rId35" xr:uid="{FA6AA4AE-7F07-43D1-B475-ADE11A5D51B1}"/>
-    <hyperlink ref="O36" r:id="rId36" xr:uid="{73308212-AB40-4B94-A6D0-81801AA0D5F8}"/>
+    <hyperlink ref="O14" r:id="rId3" xr:uid="{42D3E95E-4A54-4681-8DD2-B405F8766920}"/>
+    <hyperlink ref="O15" r:id="rId4" xr:uid="{84858A17-343C-4382-89D9-8E88B2679CF6}"/>
+    <hyperlink ref="O16" r:id="rId5" xr:uid="{1D42C161-9348-4E50-8829-4A2AB74BE576}"/>
+    <hyperlink ref="O17" r:id="rId6" xr:uid="{77D8AFD1-CA93-40B0-9AB1-01AFA20E8CBF}"/>
+    <hyperlink ref="O18" r:id="rId7" xr:uid="{022A5E50-C635-4680-A1A7-9FD01AB2DCB9}"/>
+    <hyperlink ref="O19" r:id="rId8" xr:uid="{AF8FC433-8557-4930-9F93-B0BDC0D93633}"/>
+    <hyperlink ref="O20" r:id="rId9" xr:uid="{5D8D396A-4B9E-4433-AC86-359BF9C2E836}"/>
+    <hyperlink ref="O21" r:id="rId10" xr:uid="{24AD814A-F8AC-44A9-A96B-512C2D4D4A9E}"/>
+    <hyperlink ref="O23" r:id="rId11" xr:uid="{05628E33-6E5F-4008-A818-B731C118EC5E}"/>
+    <hyperlink ref="O24" r:id="rId12" xr:uid="{88128F9D-7EFF-4D52-87D7-9ABB22B3FE7D}"/>
+    <hyperlink ref="O33" r:id="rId13" xr:uid="{991349B4-FA5F-46BE-92E5-E5228174FB13}"/>
+    <hyperlink ref="O34" r:id="rId14" xr:uid="{D20CC96C-F0B2-4507-9A17-C43EF77BFED5}"/>
+    <hyperlink ref="O35" r:id="rId15" xr:uid="{C31D8FA7-31D2-4F7A-AAF2-A35193C83DEB}"/>
+    <hyperlink ref="O37" r:id="rId16" xr:uid="{108D1389-3DE9-4341-B4CD-5862FD176D0E}"/>
+    <hyperlink ref="O39" r:id="rId17" xr:uid="{078D3269-7E5E-40E1-AA3C-DA4DE0F331AB}"/>
+    <hyperlink ref="O40" r:id="rId18" xr:uid="{FB1093E0-651D-429A-8ECF-27D6532353DA}"/>
+    <hyperlink ref="O41" r:id="rId19" xr:uid="{71099F03-EFD3-4608-B59C-4F7AE5EF6DBF}"/>
+    <hyperlink ref="O42" r:id="rId20" xr:uid="{237BD033-D3F3-4E5B-9D55-F222CBCDA51A}"/>
+    <hyperlink ref="O43" r:id="rId21" xr:uid="{ABA061C0-3178-4EEE-AC9E-00F3074CCA83}"/>
+    <hyperlink ref="O44" r:id="rId22" xr:uid="{E3D102C8-0F26-49E0-9DD2-8086B665C1A9}"/>
+    <hyperlink ref="O45" r:id="rId23" xr:uid="{5F351CAB-DED2-4547-A277-A2BD52DD8FA7}"/>
+    <hyperlink ref="O48" r:id="rId24" xr:uid="{2E5DC74F-6A03-4F11-A724-94718B7221E7}"/>
+    <hyperlink ref="O11" r:id="rId25" xr:uid="{9E8A17B7-5D2F-4C74-B22B-A47931EE4D28}"/>
+    <hyperlink ref="O22" r:id="rId26" xr:uid="{0D6B720F-74DB-4906-B7E4-12F9EBBB2CD7}"/>
+    <hyperlink ref="O26" r:id="rId27" xr:uid="{E6C2E888-5DFE-4518-B9DA-59675AD20B1F}"/>
+    <hyperlink ref="O27" r:id="rId28" xr:uid="{7F9E98A4-2FC1-4E25-8EFE-AC9AD2673293}"/>
+    <hyperlink ref="O28" r:id="rId29" xr:uid="{7B2A4AC0-A421-4755-B302-91033C8526E7}"/>
+    <hyperlink ref="O30" r:id="rId30" xr:uid="{1566147B-6D46-410E-9332-C2A8C56F7EF8}"/>
+    <hyperlink ref="O31" r:id="rId31" xr:uid="{B2A3A2E4-A598-499D-8F57-43F54F143C2A}"/>
+    <hyperlink ref="O25" r:id="rId32" xr:uid="{D6A67807-A726-4FC2-AE6E-F7CFE64FA5E5}"/>
+    <hyperlink ref="O38" r:id="rId33" xr:uid="{FA6AA4AE-7F07-43D1-B475-ADE11A5D51B1}"/>
+    <hyperlink ref="O36" r:id="rId34" xr:uid="{73308212-AB40-4B94-A6D0-81801AA0D5F8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId37"/>
-  <drawing r:id="rId38"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId35"/>
+  <drawing r:id="rId36"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -4929,6 +4998,58 @@
           </x14:cfRule>
           <xm:sqref>O25</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{C425534F-2132-4E3E-9E27-4731DA9BFCD1}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>O29</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{66F3904F-387C-4CAD-BEC6-08FB3198833C}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>O47</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{0840C77E-1C20-4E52-9B84-C937166616D1}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>O49</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{A36A295E-890B-44B2-8B87-7FA091974DAC}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>O13</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/Deliverables/Interface_Board/BOM/Interface_Board_BOM Quantity(500).xlsx
+++ b/Deliverables/Interface_Board/BOM/Interface_Board_BOM Quantity(500).xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ChristianRaun-EthercatDesign\Deliverables\Interface_Board\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ChristianRaun-EthercatDesign\Deliverables\Interface_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B33E60E-95C2-4257-A4BA-8AE873376A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="269">
   <si>
     <t>Component list</t>
   </si>
@@ -838,12 +837,15 @@
   </si>
   <si>
     <t>Karen Quotes</t>
+  </si>
+  <si>
+    <t>This header will be sourced in Control Board BOM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -1715,6 +1717,15 @@
     <xf numFmtId="0" fontId="22" fillId="2" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1749,15 +1760,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1804,7 +1806,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2100,7 +2102,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2136,15 +2138,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="119"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="122"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2194,7 +2196,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="120"/>
+      <c r="S3" s="123"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2219,7 +2221,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="121"/>
+      <c r="S4" s="124"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2244,7 +2246,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="121"/>
+      <c r="S5" s="124"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2265,7 +2267,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="121"/>
+      <c r="S6" s="124"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2286,7 +2288,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="121"/>
+      <c r="S7" s="124"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2307,7 +2309,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="121"/>
+      <c r="S8" s="124"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2372,7 +2374,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="129" t="s">
+      <c r="C10" s="118" t="s">
         <v>248</v>
       </c>
       <c r="D10" s="41" t="s">
@@ -2428,7 +2430,7 @@
         <f t="shared" ref="B11:B49" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="130"/>
+      <c r="C11" s="119"/>
       <c r="D11" s="45" t="s">
         <v>12</v>
       </c>
@@ -2482,7 +2484,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="130"/>
+      <c r="C12" s="119"/>
       <c r="D12" s="41" t="s">
         <v>13</v>
       </c>
@@ -2536,7 +2538,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="130"/>
+      <c r="C13" s="119"/>
       <c r="D13" s="45" t="s">
         <v>14</v>
       </c>
@@ -2592,7 +2594,7 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="130"/>
+      <c r="C14" s="119"/>
       <c r="D14" s="41" t="s">
         <v>15</v>
       </c>
@@ -2646,7 +2648,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="130"/>
+      <c r="C15" s="119"/>
       <c r="D15" s="45" t="s">
         <v>16</v>
       </c>
@@ -2700,7 +2702,7 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="130"/>
+      <c r="C16" s="119"/>
       <c r="D16" s="41" t="s">
         <v>17</v>
       </c>
@@ -2754,7 +2756,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="130"/>
+      <c r="C17" s="119"/>
       <c r="D17" s="45" t="s">
         <v>18</v>
       </c>
@@ -2808,7 +2810,7 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="130"/>
+      <c r="C18" s="119"/>
       <c r="D18" s="41" t="s">
         <v>19</v>
       </c>
@@ -2862,7 +2864,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="130"/>
+      <c r="C19" s="119"/>
       <c r="D19" s="45" t="s">
         <v>20</v>
       </c>
@@ -2916,7 +2918,7 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="131"/>
+      <c r="C20" s="120"/>
       <c r="D20" s="41" t="s">
         <v>21</v>
       </c>
@@ -2972,7 +2974,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="130" t="s">
+      <c r="C21" s="119" t="s">
         <v>249</v>
       </c>
       <c r="D21" s="45" t="s">
@@ -3028,7 +3030,7 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="130"/>
+      <c r="C22" s="119"/>
       <c r="D22" s="41" t="s">
         <v>23</v>
       </c>
@@ -3082,7 +3084,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="130"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="45" t="s">
         <v>24</v>
       </c>
@@ -3136,7 +3138,7 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="130"/>
+      <c r="C24" s="119"/>
       <c r="D24" s="41" t="s">
         <v>25</v>
       </c>
@@ -3190,7 +3192,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="129" t="s">
+      <c r="C25" s="118" t="s">
         <v>250</v>
       </c>
       <c r="D25" s="45" t="s">
@@ -3246,7 +3248,7 @@
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="130"/>
+      <c r="C26" s="119"/>
       <c r="D26" s="41" t="s">
         <v>27</v>
       </c>
@@ -3294,13 +3296,13 @@
       <c r="R26" s="41"/>
       <c r="S26" s="57"/>
     </row>
-    <row r="27" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="36">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="131"/>
+      <c r="C27" s="120"/>
       <c r="D27" s="45" t="s">
         <v>28</v>
       </c>
@@ -3335,18 +3337,13 @@
       <c r="N27" s="47">
         <v>510</v>
       </c>
-      <c r="O27" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="P27" s="89">
-        <v>0.16800000000000001</v>
-      </c>
-      <c r="Q27" s="54">
-        <f t="shared" si="2"/>
-        <v>85.68</v>
-      </c>
+      <c r="O27" s="55"/>
+      <c r="P27" s="89"/>
+      <c r="Q27" s="54"/>
       <c r="R27" s="45"/>
-      <c r="S27" s="49"/>
+      <c r="S27" s="114" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
@@ -3354,7 +3351,7 @@
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="129" t="s">
+      <c r="C28" s="118" t="s">
         <v>251</v>
       </c>
       <c r="D28" s="41" t="s">
@@ -3410,7 +3407,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="131"/>
+      <c r="C29" s="120"/>
       <c r="D29" s="45" t="s">
         <v>30</v>
       </c>
@@ -3466,7 +3463,7 @@
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="129" t="s">
+      <c r="C30" s="118" t="s">
         <v>250</v>
       </c>
       <c r="D30" s="41" t="s">
@@ -3522,7 +3519,7 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="130"/>
+      <c r="C31" s="119"/>
       <c r="D31" s="45" t="s">
         <v>32</v>
       </c>
@@ -3747,7 +3744,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="129" t="s">
+      <c r="C35" s="118" t="s">
         <v>254</v>
       </c>
       <c r="D35" s="45" t="s">
@@ -3803,7 +3800,7 @@
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="130"/>
+      <c r="C36" s="119"/>
       <c r="D36" s="41" t="s">
         <v>37</v>
       </c>
@@ -3857,7 +3854,7 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="130"/>
+      <c r="C37" s="119"/>
       <c r="D37" s="45" t="s">
         <v>38</v>
       </c>
@@ -3911,7 +3908,7 @@
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="130"/>
+      <c r="C38" s="119"/>
       <c r="D38" s="41" t="s">
         <v>39</v>
       </c>
@@ -3965,7 +3962,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="130"/>
+      <c r="C39" s="119"/>
       <c r="D39" s="45" t="s">
         <v>40</v>
       </c>
@@ -4019,7 +4016,7 @@
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="130"/>
+      <c r="C40" s="119"/>
       <c r="D40" s="41" t="s">
         <v>41</v>
       </c>
@@ -4073,7 +4070,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="130"/>
+      <c r="C41" s="119"/>
       <c r="D41" s="45" t="s">
         <v>42</v>
       </c>
@@ -4127,7 +4124,7 @@
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="130"/>
+      <c r="C42" s="119"/>
       <c r="D42" s="41" t="s">
         <v>43</v>
       </c>
@@ -4181,7 +4178,7 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="130"/>
+      <c r="C43" s="119"/>
       <c r="D43" s="45" t="s">
         <v>44</v>
       </c>
@@ -4235,7 +4232,7 @@
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="130"/>
+      <c r="C44" s="119"/>
       <c r="D44" s="41" t="s">
         <v>45</v>
       </c>
@@ -4289,7 +4286,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="131"/>
+      <c r="C45" s="120"/>
       <c r="D45" s="45" t="s">
         <v>46</v>
       </c>
@@ -4402,7 +4399,7 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="130" t="s">
+      <c r="C47" s="119" t="s">
         <v>255</v>
       </c>
       <c r="D47" s="45" t="s">
@@ -4460,7 +4457,7 @@
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
-      <c r="C48" s="130"/>
+      <c r="C48" s="119"/>
       <c r="D48" s="41" t="s">
         <v>49</v>
       </c>
@@ -4514,7 +4511,7 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="131"/>
+      <c r="C49" s="120"/>
       <c r="D49" s="45" t="s">
         <v>50</v>
       </c>
@@ -4580,17 +4577,17 @@
       <c r="K50" s="35"/>
       <c r="L50" s="35"/>
       <c r="M50" s="107"/>
-      <c r="N50" s="122" t="s">
+      <c r="N50" s="125" t="s">
         <v>243</v>
       </c>
-      <c r="O50" s="123"/>
-      <c r="P50" s="123"/>
+      <c r="O50" s="126"/>
+      <c r="P50" s="126"/>
       <c r="Q50" s="85">
         <f>SUM(Q10:Q49)</f>
-        <v>6275.7455000000009</v>
-      </c>
-      <c r="R50" s="125"/>
-      <c r="S50" s="126"/>
+        <v>6190.0655000000006</v>
+      </c>
+      <c r="R50" s="128"/>
+      <c r="S50" s="129"/>
     </row>
     <row r="51" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
@@ -4608,16 +4605,16 @@
       <c r="K51" s="112"/>
       <c r="L51" s="112"/>
       <c r="M51" s="113"/>
-      <c r="N51" s="122" t="s">
+      <c r="N51" s="125" t="s">
         <v>245</v>
       </c>
-      <c r="O51" s="123"/>
-      <c r="P51" s="124"/>
+      <c r="O51" s="126"/>
+      <c r="P51" s="127"/>
       <c r="Q51" s="87">
         <v>67.599999999999994</v>
       </c>
-      <c r="R51" s="127"/>
-      <c r="S51" s="128"/>
+      <c r="R51" s="130"/>
+      <c r="S51" s="131"/>
     </row>
     <row r="52" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
@@ -4631,18 +4628,24 @@
       <c r="K52" s="24"/>
       <c r="L52" s="24"/>
       <c r="M52" s="24"/>
-      <c r="N52" s="122" t="s">
+      <c r="N52" s="125" t="s">
         <v>244</v>
       </c>
-      <c r="O52" s="123"/>
-      <c r="P52" s="123"/>
+      <c r="O52" s="126"/>
+      <c r="P52" s="126"/>
       <c r="Q52" s="86">
         <f>Q50/500</f>
-        <v>12.551491000000002</v>
+        <v>12.380131</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R50:S51"/>
     <mergeCell ref="C35:C45"/>
     <mergeCell ref="C47:C49"/>
     <mergeCell ref="C10:C20"/>
@@ -4650,12 +4653,6 @@
     <mergeCell ref="C25:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R50:S51"/>
   </mergeCells>
   <conditionalFormatting sqref="O14">
     <cfRule type="dataBar" priority="15">
@@ -4840,44 +4837,42 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1" xr:uid="{1B6B54E8-03CF-40A3-B32B-4151F2017DDB}"/>
-    <hyperlink ref="O12" r:id="rId2" xr:uid="{A6AF3D12-A2B7-406C-99DE-4A2B14492EBF}"/>
-    <hyperlink ref="O14" r:id="rId3" xr:uid="{42D3E95E-4A54-4681-8DD2-B405F8766920}"/>
-    <hyperlink ref="O15" r:id="rId4" xr:uid="{84858A17-343C-4382-89D9-8E88B2679CF6}"/>
-    <hyperlink ref="O16" r:id="rId5" xr:uid="{1D42C161-9348-4E50-8829-4A2AB74BE576}"/>
-    <hyperlink ref="O17" r:id="rId6" xr:uid="{77D8AFD1-CA93-40B0-9AB1-01AFA20E8CBF}"/>
-    <hyperlink ref="O18" r:id="rId7" xr:uid="{022A5E50-C635-4680-A1A7-9FD01AB2DCB9}"/>
-    <hyperlink ref="O19" r:id="rId8" xr:uid="{AF8FC433-8557-4930-9F93-B0BDC0D93633}"/>
-    <hyperlink ref="O20" r:id="rId9" xr:uid="{5D8D396A-4B9E-4433-AC86-359BF9C2E836}"/>
-    <hyperlink ref="O21" r:id="rId10" xr:uid="{24AD814A-F8AC-44A9-A96B-512C2D4D4A9E}"/>
-    <hyperlink ref="O23" r:id="rId11" xr:uid="{05628E33-6E5F-4008-A818-B731C118EC5E}"/>
-    <hyperlink ref="O24" r:id="rId12" xr:uid="{88128F9D-7EFF-4D52-87D7-9ABB22B3FE7D}"/>
-    <hyperlink ref="O33" r:id="rId13" xr:uid="{991349B4-FA5F-46BE-92E5-E5228174FB13}"/>
-    <hyperlink ref="O34" r:id="rId14" xr:uid="{D20CC96C-F0B2-4507-9A17-C43EF77BFED5}"/>
-    <hyperlink ref="O35" r:id="rId15" xr:uid="{C31D8FA7-31D2-4F7A-AAF2-A35193C83DEB}"/>
-    <hyperlink ref="O37" r:id="rId16" xr:uid="{108D1389-3DE9-4341-B4CD-5862FD176D0E}"/>
-    <hyperlink ref="O39" r:id="rId17" xr:uid="{078D3269-7E5E-40E1-AA3C-DA4DE0F331AB}"/>
-    <hyperlink ref="O40" r:id="rId18" xr:uid="{FB1093E0-651D-429A-8ECF-27D6532353DA}"/>
-    <hyperlink ref="O41" r:id="rId19" xr:uid="{71099F03-EFD3-4608-B59C-4F7AE5EF6DBF}"/>
-    <hyperlink ref="O42" r:id="rId20" xr:uid="{237BD033-D3F3-4E5B-9D55-F222CBCDA51A}"/>
-    <hyperlink ref="O43" r:id="rId21" xr:uid="{ABA061C0-3178-4EEE-AC9E-00F3074CCA83}"/>
-    <hyperlink ref="O44" r:id="rId22" xr:uid="{E3D102C8-0F26-49E0-9DD2-8086B665C1A9}"/>
-    <hyperlink ref="O45" r:id="rId23" xr:uid="{5F351CAB-DED2-4547-A277-A2BD52DD8FA7}"/>
-    <hyperlink ref="O48" r:id="rId24" xr:uid="{2E5DC74F-6A03-4F11-A724-94718B7221E7}"/>
-    <hyperlink ref="O11" r:id="rId25" xr:uid="{9E8A17B7-5D2F-4C74-B22B-A47931EE4D28}"/>
-    <hyperlink ref="O22" r:id="rId26" xr:uid="{0D6B720F-74DB-4906-B7E4-12F9EBBB2CD7}"/>
-    <hyperlink ref="O26" r:id="rId27" xr:uid="{E6C2E888-5DFE-4518-B9DA-59675AD20B1F}"/>
-    <hyperlink ref="O27" r:id="rId28" xr:uid="{7F9E98A4-2FC1-4E25-8EFE-AC9AD2673293}"/>
-    <hyperlink ref="O28" r:id="rId29" xr:uid="{7B2A4AC0-A421-4755-B302-91033C8526E7}"/>
-    <hyperlink ref="O30" r:id="rId30" xr:uid="{1566147B-6D46-410E-9332-C2A8C56F7EF8}"/>
-    <hyperlink ref="O31" r:id="rId31" xr:uid="{B2A3A2E4-A598-499D-8F57-43F54F143C2A}"/>
-    <hyperlink ref="O25" r:id="rId32" xr:uid="{D6A67807-A726-4FC2-AE6E-F7CFE64FA5E5}"/>
-    <hyperlink ref="O38" r:id="rId33" xr:uid="{FA6AA4AE-7F07-43D1-B475-ADE11A5D51B1}"/>
-    <hyperlink ref="O36" r:id="rId34" xr:uid="{73308212-AB40-4B94-A6D0-81801AA0D5F8}"/>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O12" r:id="rId2"/>
+    <hyperlink ref="O14" r:id="rId3"/>
+    <hyperlink ref="O15" r:id="rId4"/>
+    <hyperlink ref="O16" r:id="rId5"/>
+    <hyperlink ref="O17" r:id="rId6"/>
+    <hyperlink ref="O18" r:id="rId7"/>
+    <hyperlink ref="O19" r:id="rId8"/>
+    <hyperlink ref="O20" r:id="rId9"/>
+    <hyperlink ref="O21" r:id="rId10"/>
+    <hyperlink ref="O23" r:id="rId11"/>
+    <hyperlink ref="O24" r:id="rId12"/>
+    <hyperlink ref="O33" r:id="rId13"/>
+    <hyperlink ref="O34" r:id="rId14"/>
+    <hyperlink ref="O35" r:id="rId15"/>
+    <hyperlink ref="O37" r:id="rId16"/>
+    <hyperlink ref="O39" r:id="rId17"/>
+    <hyperlink ref="O40" r:id="rId18"/>
+    <hyperlink ref="O41" r:id="rId19"/>
+    <hyperlink ref="O42" r:id="rId20"/>
+    <hyperlink ref="O43" r:id="rId21"/>
+    <hyperlink ref="O44" r:id="rId22"/>
+    <hyperlink ref="O45" r:id="rId23"/>
+    <hyperlink ref="O48" r:id="rId24"/>
+    <hyperlink ref="O11" r:id="rId25"/>
+    <hyperlink ref="O22" r:id="rId26"/>
+    <hyperlink ref="O26" r:id="rId27"/>
+    <hyperlink ref="O30" r:id="rId28"/>
+    <hyperlink ref="O31" r:id="rId29"/>
+    <hyperlink ref="O25" r:id="rId30"/>
+    <hyperlink ref="O38" r:id="rId31"/>
+    <hyperlink ref="O36" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId35"/>
-  <drawing r:id="rId36"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId33"/>
+  <drawing r:id="rId34"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>

--- a/Deliverables/Interface_Board/BOM/Interface_Board_BOM Quantity(500).xlsx
+++ b/Deliverables/Interface_Board/BOM/Interface_Board_BOM Quantity(500).xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="270">
   <si>
     <t>Component list</t>
   </si>
@@ -803,9 +803,6 @@
     <t>IC</t>
   </si>
   <si>
-    <t xml:space="preserve">Is Part ki cost zayada ha kia hum is part ko local part se replays kr sakte han </t>
-  </si>
-  <si>
     <t>ARG05BTC9001N</t>
   </si>
   <si>
@@ -840,6 +837,12 @@
   </si>
   <si>
     <t>This header will be sourced in Control Board BOM</t>
+  </si>
+  <si>
+    <t>1 x 13p 510 pcs ordered from LCSC</t>
+  </si>
+  <si>
+    <t>2 x 13p 6 lots (100pcs / lot) ordered</t>
   </si>
 </sst>
 </file>
@@ -851,7 +854,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1034,14 +1037,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1388,7 +1383,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1596,12 +1591,6 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="18" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="20" fillId="4" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1711,19 +1700,7 @@
     <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1761,6 +1738,42 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1806,7 +1819,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2138,20 +2151,20 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="122"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="116"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
-      <c r="C2" s="90"/>
+      <c r="C2" s="88"/>
       <c r="D2" s="10" t="s">
         <v>0</v>
       </c>
@@ -2176,7 +2189,7 @@
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
-      <c r="C3" s="91"/>
+      <c r="C3" s="89"/>
       <c r="D3" s="12" t="s">
         <v>1</v>
       </c>
@@ -2196,12 +2209,12 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="123"/>
+      <c r="S3" s="117"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
-      <c r="C4" s="91"/>
+      <c r="C4" s="89"/>
       <c r="D4" s="12" t="s">
         <v>2</v>
       </c>
@@ -2221,12 +2234,12 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="124"/>
+      <c r="S4" s="118"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
-      <c r="C5" s="91"/>
+      <c r="C5" s="89"/>
       <c r="D5" s="12" t="s">
         <v>3</v>
       </c>
@@ -2246,12 +2259,12 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="124"/>
+      <c r="S5" s="118"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
-      <c r="C6" s="92"/>
+      <c r="C6" s="90"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="16"/>
@@ -2267,12 +2280,12 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="124"/>
+      <c r="S6" s="118"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
-      <c r="C7" s="93"/>
+      <c r="C7" s="91"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
@@ -2288,12 +2301,12 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="124"/>
+      <c r="S7" s="118"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="25"/>
-      <c r="C8" s="94"/>
+      <c r="C8" s="92"/>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
       <c r="F8" s="27"/>
@@ -2309,7 +2322,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="124"/>
+      <c r="S8" s="118"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2350,7 +2363,7 @@
         <v>191</v>
       </c>
       <c r="N9" s="28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O9" s="28" t="s">
         <v>192</v>
@@ -2374,7 +2387,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="118" t="s">
+      <c r="C10" s="126" t="s">
         <v>248</v>
       </c>
       <c r="D10" s="41" t="s">
@@ -2414,7 +2427,7 @@
       <c r="O10" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="P10" s="104">
+      <c r="P10" s="102">
         <v>2.3199999999999998E-2</v>
       </c>
       <c r="Q10" s="51">
@@ -2430,7 +2443,7 @@
         <f t="shared" ref="B11:B49" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="119"/>
+      <c r="C11" s="127"/>
       <c r="D11" s="45" t="s">
         <v>12</v>
       </c>
@@ -2440,7 +2453,7 @@
       <c r="F11" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="G11" s="101" t="s">
+      <c r="G11" s="99" t="s">
         <v>120</v>
       </c>
       <c r="H11" s="45" t="s">
@@ -2468,7 +2481,7 @@
       <c r="O11" s="64" t="s">
         <v>197</v>
       </c>
-      <c r="P11" s="89">
+      <c r="P11" s="87">
         <v>1.4200000000000001E-2</v>
       </c>
       <c r="Q11" s="54">
@@ -2484,7 +2497,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="119"/>
+      <c r="C12" s="127"/>
       <c r="D12" s="41" t="s">
         <v>13</v>
       </c>
@@ -2522,7 +2535,7 @@
       <c r="O12" s="71" t="s">
         <v>197</v>
       </c>
-      <c r="P12" s="104">
+      <c r="P12" s="102">
         <v>7.3599999999999999E-2</v>
       </c>
       <c r="Q12" s="51">
@@ -2538,7 +2551,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="119"/>
+      <c r="C13" s="127"/>
       <c r="D13" s="45" t="s">
         <v>14</v>
       </c>
@@ -2574,17 +2587,17 @@
         <v>1520</v>
       </c>
       <c r="O13" s="75" t="s">
-        <v>266</v>
-      </c>
-      <c r="P13" s="89">
+        <v>265</v>
+      </c>
+      <c r="P13" s="87">
         <v>0.1</v>
       </c>
       <c r="Q13" s="54">
         <f t="shared" si="2"/>
         <v>152</v>
       </c>
-      <c r="R13" s="114" t="s">
-        <v>267</v>
+      <c r="R13" s="112" t="s">
+        <v>266</v>
       </c>
       <c r="S13" s="49"/>
     </row>
@@ -2594,7 +2607,7 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="119"/>
+      <c r="C14" s="127"/>
       <c r="D14" s="41" t="s">
         <v>15</v>
       </c>
@@ -2632,7 +2645,7 @@
       <c r="O14" s="73" t="s">
         <v>197</v>
       </c>
-      <c r="P14" s="104">
+      <c r="P14" s="102">
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="Q14" s="51">
@@ -2648,7 +2661,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="119"/>
+      <c r="C15" s="127"/>
       <c r="D15" s="45" t="s">
         <v>16</v>
       </c>
@@ -2658,7 +2671,7 @@
       <c r="F15" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="G15" s="101" t="s">
+      <c r="G15" s="99" t="s">
         <v>122</v>
       </c>
       <c r="H15" s="45" t="s">
@@ -2686,7 +2699,7 @@
       <c r="O15" s="74" t="s">
         <v>197</v>
       </c>
-      <c r="P15" s="89">
+      <c r="P15" s="87">
         <v>2.5999999999999999E-3</v>
       </c>
       <c r="Q15" s="54">
@@ -2702,7 +2715,7 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="119"/>
+      <c r="C16" s="127"/>
       <c r="D16" s="41" t="s">
         <v>17</v>
       </c>
@@ -2712,7 +2725,7 @@
       <c r="F16" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="G16" s="102" t="s">
+      <c r="G16" s="100" t="s">
         <v>123</v>
       </c>
       <c r="H16" s="65" t="s">
@@ -2740,7 +2753,7 @@
       <c r="O16" s="71" t="s">
         <v>197</v>
       </c>
-      <c r="P16" s="104">
+      <c r="P16" s="102">
         <v>4.7999999999999996E-3</v>
       </c>
       <c r="Q16" s="51">
@@ -2756,7 +2769,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="119"/>
+      <c r="C17" s="127"/>
       <c r="D17" s="45" t="s">
         <v>18</v>
       </c>
@@ -2794,7 +2807,7 @@
       <c r="O17" s="64" t="s">
         <v>197</v>
       </c>
-      <c r="P17" s="89">
+      <c r="P17" s="87">
         <v>9.4999999999999998E-3</v>
       </c>
       <c r="Q17" s="54">
@@ -2810,7 +2823,7 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="119"/>
+      <c r="C18" s="127"/>
       <c r="D18" s="41" t="s">
         <v>19</v>
       </c>
@@ -2848,7 +2861,7 @@
       <c r="O18" s="73" t="s">
         <v>197</v>
       </c>
-      <c r="P18" s="104">
+      <c r="P18" s="102">
         <v>4.7999999999999996E-3</v>
       </c>
       <c r="Q18" s="51">
@@ -2864,7 +2877,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="119"/>
+      <c r="C19" s="127"/>
       <c r="D19" s="45" t="s">
         <v>20</v>
       </c>
@@ -2902,7 +2915,7 @@
       <c r="O19" s="75" t="s">
         <v>197</v>
       </c>
-      <c r="P19" s="89">
+      <c r="P19" s="87">
         <v>1.6400000000000001E-2</v>
       </c>
       <c r="Q19" s="54">
@@ -2918,7 +2931,7 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="120"/>
+      <c r="C20" s="128"/>
       <c r="D20" s="41" t="s">
         <v>21</v>
       </c>
@@ -2956,14 +2969,14 @@
       <c r="O20" s="73" t="s">
         <v>197</v>
       </c>
-      <c r="P20" s="104">
+      <c r="P20" s="102">
         <v>7.7200000000000005E-2</v>
       </c>
       <c r="Q20" s="51">
         <f t="shared" si="2"/>
         <v>78.744</v>
       </c>
-      <c r="R20" s="115" t="s">
+      <c r="R20" s="113" t="s">
         <v>204</v>
       </c>
       <c r="S20" s="57"/>
@@ -2974,7 +2987,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="119" t="s">
+      <c r="C21" s="127" t="s">
         <v>249</v>
       </c>
       <c r="D21" s="45" t="s">
@@ -3014,7 +3027,7 @@
       <c r="O21" s="75" t="s">
         <v>197</v>
       </c>
-      <c r="P21" s="89">
+      <c r="P21" s="87">
         <v>0.26669999999999999</v>
       </c>
       <c r="Q21" s="54">
@@ -3030,7 +3043,7 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="119"/>
+      <c r="C22" s="127"/>
       <c r="D22" s="41" t="s">
         <v>23</v>
       </c>
@@ -3068,14 +3081,14 @@
       <c r="O22" s="67" t="s">
         <v>197</v>
       </c>
-      <c r="P22" s="104">
+      <c r="P22" s="102">
         <v>2.6100000000000002E-2</v>
       </c>
       <c r="Q22" s="51">
         <f t="shared" si="2"/>
         <v>13.572000000000001</v>
       </c>
-      <c r="R22" s="115"/>
+      <c r="R22" s="113"/>
       <c r="S22" s="57"/>
     </row>
     <row r="23" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3084,7 +3097,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="119"/>
+      <c r="C23" s="127"/>
       <c r="D23" s="45" t="s">
         <v>24</v>
       </c>
@@ -3122,7 +3135,7 @@
       <c r="O23" s="75" t="s">
         <v>197</v>
       </c>
-      <c r="P23" s="89">
+      <c r="P23" s="87">
         <v>1.78E-2</v>
       </c>
       <c r="Q23" s="54">
@@ -3138,7 +3151,7 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="119"/>
+      <c r="C24" s="127"/>
       <c r="D24" s="41" t="s">
         <v>25</v>
       </c>
@@ -3176,7 +3189,7 @@
       <c r="O24" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="P24" s="104">
+      <c r="P24" s="102">
         <v>5.6599999999999998E-2</v>
       </c>
       <c r="Q24" s="51">
@@ -3192,16 +3205,16 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="118" t="s">
+      <c r="C25" s="126" t="s">
         <v>250</v>
       </c>
       <c r="D25" s="45" t="s">
         <v>26</v>
       </c>
       <c r="E25" s="45" t="s">
-        <v>263</v>
-      </c>
-      <c r="F25" s="98" t="s">
+        <v>262</v>
+      </c>
+      <c r="F25" s="96" t="s">
         <v>201</v>
       </c>
       <c r="G25" s="45" t="s">
@@ -3227,20 +3240,22 @@
         <v>500</v>
       </c>
       <c r="N25" s="47">
-        <v>600</v>
+        <v>6</v>
       </c>
       <c r="O25" s="75" t="s">
         <v>239</v>
       </c>
-      <c r="P25" s="89">
-        <v>0.32579999999999998</v>
+      <c r="P25" s="87">
+        <v>35</v>
       </c>
       <c r="Q25" s="54">
-        <f t="shared" si="2"/>
-        <v>195.48</v>
+        <f>P25*N25</f>
+        <v>210</v>
       </c>
       <c r="R25" s="45"/>
-      <c r="S25" s="49"/>
+      <c r="S25" s="112" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="26" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
@@ -3248,14 +3263,14 @@
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="119"/>
+      <c r="C26" s="127"/>
       <c r="D26" s="41" t="s">
         <v>27</v>
       </c>
       <c r="E26" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="F26" s="99" t="s">
+      <c r="F26" s="97" t="s">
         <v>201</v>
       </c>
       <c r="G26" s="41" t="s">
@@ -3286,7 +3301,7 @@
       <c r="O26" s="63" t="s">
         <v>197</v>
       </c>
-      <c r="P26" s="104">
+      <c r="P26" s="102">
         <v>1.2641</v>
       </c>
       <c r="Q26" s="51">
@@ -3302,14 +3317,14 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="120"/>
+      <c r="C27" s="128"/>
       <c r="D27" s="45" t="s">
         <v>28</v>
       </c>
       <c r="E27" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="F27" s="98" t="s">
+      <c r="F27" s="96" t="s">
         <v>201</v>
       </c>
       <c r="G27" s="45" t="s">
@@ -3338,11 +3353,11 @@
         <v>510</v>
       </c>
       <c r="O27" s="55"/>
-      <c r="P27" s="89"/>
+      <c r="P27" s="87"/>
       <c r="Q27" s="54"/>
       <c r="R27" s="45"/>
-      <c r="S27" s="114" t="s">
-        <v>268</v>
+      <c r="S27" s="112" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3351,7 +3366,7 @@
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="118" t="s">
+      <c r="C28" s="126" t="s">
         <v>251</v>
       </c>
       <c r="D28" s="41" t="s">
@@ -3360,7 +3375,7 @@
       <c r="E28" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="F28" s="99" t="s">
+      <c r="F28" s="97" t="s">
         <v>201</v>
       </c>
       <c r="G28" s="41" t="s">
@@ -3391,7 +3406,7 @@
       <c r="O28" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="P28" s="104">
+      <c r="P28" s="102">
         <v>3.8600000000000002E-2</v>
       </c>
       <c r="Q28" s="51">
@@ -3407,7 +3422,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="120"/>
+      <c r="C29" s="128"/>
       <c r="D29" s="45" t="s">
         <v>30</v>
       </c>
@@ -3443,17 +3458,17 @@
         <v>505</v>
       </c>
       <c r="O29" s="75" t="s">
-        <v>266</v>
-      </c>
-      <c r="P29" s="89">
+        <v>265</v>
+      </c>
+      <c r="P29" s="87">
         <v>0.73</v>
       </c>
       <c r="Q29" s="54">
         <f t="shared" si="2"/>
         <v>368.65</v>
       </c>
-      <c r="R29" s="114" t="s">
-        <v>267</v>
+      <c r="R29" s="112" t="s">
+        <v>266</v>
       </c>
       <c r="S29" s="49"/>
     </row>
@@ -3463,7 +3478,7 @@
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="118" t="s">
+      <c r="C30" s="126" t="s">
         <v>250</v>
       </c>
       <c r="D30" s="41" t="s">
@@ -3497,29 +3512,31 @@
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N30" s="41">
-        <v>520</v>
-      </c>
-      <c r="O30" s="77" t="s">
+      <c r="N30" s="130">
+        <v>500</v>
+      </c>
+      <c r="O30" s="131" t="s">
         <v>197</v>
       </c>
-      <c r="P30" s="104">
-        <v>2.47E-2</v>
-      </c>
-      <c r="Q30" s="51">
-        <f t="shared" si="2"/>
-        <v>12.843999999999999</v>
-      </c>
-      <c r="R30" s="41"/>
-      <c r="S30" s="57"/>
-    </row>
-    <row r="31" spans="1:19" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P30" s="133">
+        <v>8.8400000000000006E-2</v>
+      </c>
+      <c r="Q30" s="135">
+        <f>P30*N30</f>
+        <v>44.2</v>
+      </c>
+      <c r="R30" s="130"/>
+      <c r="S30" s="136" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="36">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="119"/>
+      <c r="C31" s="127"/>
       <c r="D31" s="45" t="s">
         <v>32</v>
       </c>
@@ -3551,23 +3568,12 @@
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N31" s="47">
-        <v>1005</v>
-      </c>
-      <c r="O31" s="78" t="s">
-        <v>197</v>
-      </c>
-      <c r="P31" s="89">
-        <v>0.20269999999999999</v>
-      </c>
-      <c r="Q31" s="54">
-        <f t="shared" si="2"/>
-        <v>203.71349999999998</v>
-      </c>
-      <c r="R31" s="116" t="s">
-        <v>256</v>
-      </c>
-      <c r="S31" s="49"/>
+      <c r="N31" s="129"/>
+      <c r="O31" s="132"/>
+      <c r="P31" s="134"/>
+      <c r="Q31" s="134"/>
+      <c r="R31" s="129"/>
+      <c r="S31" s="137"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
@@ -3575,8 +3581,8 @@
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="97" t="s">
-        <v>265</v>
+      <c r="C32" s="95" t="s">
+        <v>264</v>
       </c>
       <c r="D32" s="41" t="s">
         <v>33</v>
@@ -3621,7 +3627,7 @@
       <c r="Q32" s="56" t="s">
         <v>202</v>
       </c>
-      <c r="R32" s="117" t="s">
+      <c r="R32" s="114" t="s">
         <v>231</v>
       </c>
       <c r="S32" s="57"/>
@@ -3632,7 +3638,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="96" t="s">
+      <c r="C33" s="94" t="s">
         <v>252</v>
       </c>
       <c r="D33" s="45" t="s">
@@ -3644,7 +3650,7 @@
       <c r="F33" s="46" t="s">
         <v>201</v>
       </c>
-      <c r="G33" s="103" t="s">
+      <c r="G33" s="101" t="s">
         <v>108</v>
       </c>
       <c r="H33" s="53" t="s">
@@ -3669,10 +3675,10 @@
       <c r="N33" s="45">
         <v>510</v>
       </c>
-      <c r="O33" s="79" t="s">
+      <c r="O33" s="77" t="s">
         <v>197</v>
       </c>
-      <c r="P33" s="89">
+      <c r="P33" s="87">
         <v>0.56630000000000003</v>
       </c>
       <c r="Q33" s="54">
@@ -3688,7 +3694,7 @@
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="97" t="s">
+      <c r="C34" s="95" t="s">
         <v>253</v>
       </c>
       <c r="D34" s="41" t="s">
@@ -3728,7 +3734,7 @@
       <c r="O34" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="P34" s="104">
+      <c r="P34" s="102">
         <v>4.4699999999999997E-2</v>
       </c>
       <c r="Q34" s="51">
@@ -3744,7 +3750,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="118" t="s">
+      <c r="C35" s="126" t="s">
         <v>254</v>
       </c>
       <c r="D35" s="45" t="s">
@@ -3781,10 +3787,10 @@
       <c r="N35" s="47">
         <v>1600</v>
       </c>
-      <c r="O35" s="80" t="s">
+      <c r="O35" s="78" t="s">
         <v>197</v>
       </c>
-      <c r="P35" s="89">
+      <c r="P35" s="87">
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="Q35" s="54">
@@ -3800,7 +3806,7 @@
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="119"/>
+      <c r="C36" s="127"/>
       <c r="D36" s="41" t="s">
         <v>37</v>
       </c>
@@ -3810,17 +3816,17 @@
       <c r="F36" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G36" s="102" t="s">
+      <c r="G36" s="100" t="s">
         <v>130</v>
       </c>
       <c r="H36" s="41" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I36" s="43" t="s">
         <v>153</v>
       </c>
       <c r="J36" s="41" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K36" s="41" t="s">
         <v>178</v>
@@ -3838,7 +3844,7 @@
       <c r="O36" s="63" t="s">
         <v>197</v>
       </c>
-      <c r="P36" s="104">
+      <c r="P36" s="102">
         <v>1.4E-3</v>
       </c>
       <c r="Q36" s="51">
@@ -3854,7 +3860,7 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="119"/>
+      <c r="C37" s="127"/>
       <c r="D37" s="45" t="s">
         <v>38</v>
       </c>
@@ -3864,7 +3870,7 @@
       <c r="F37" s="46" t="s">
         <v>111</v>
       </c>
-      <c r="G37" s="101" t="s">
+      <c r="G37" s="99" t="s">
         <v>131</v>
       </c>
       <c r="H37" s="59" t="s">
@@ -3892,7 +3898,7 @@
       <c r="O37" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="P37" s="89">
+      <c r="P37" s="87">
         <v>9.8699999999999996E-2</v>
       </c>
       <c r="Q37" s="54">
@@ -3908,7 +3914,7 @@
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="119"/>
+      <c r="C38" s="127"/>
       <c r="D38" s="41" t="s">
         <v>39</v>
       </c>
@@ -3918,17 +3924,17 @@
       <c r="F38" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="G38" s="102" t="s">
-        <v>260</v>
+      <c r="G38" s="100" t="s">
+        <v>259</v>
       </c>
       <c r="H38" s="41" t="s">
+        <v>256</v>
+      </c>
+      <c r="I38" s="43" t="s">
         <v>257</v>
       </c>
-      <c r="I38" s="43" t="s">
+      <c r="J38" s="41" t="s">
         <v>258</v>
-      </c>
-      <c r="J38" s="41" t="s">
-        <v>259</v>
       </c>
       <c r="K38" s="41" t="s">
         <v>180</v>
@@ -3946,7 +3952,7 @@
       <c r="O38" s="63" t="s">
         <v>197</v>
       </c>
-      <c r="P38" s="104">
+      <c r="P38" s="102">
         <v>3.2399999999999998E-2</v>
       </c>
       <c r="Q38" s="51">
@@ -3962,7 +3968,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="119"/>
+      <c r="C39" s="127"/>
       <c r="D39" s="45" t="s">
         <v>40</v>
       </c>
@@ -4000,7 +4006,7 @@
       <c r="O39" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="P39" s="89">
+      <c r="P39" s="87">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q39" s="54">
@@ -4016,7 +4022,7 @@
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="119"/>
+      <c r="C40" s="127"/>
       <c r="D40" s="41" t="s">
         <v>41</v>
       </c>
@@ -4051,10 +4057,10 @@
       <c r="N40" s="41">
         <v>4100</v>
       </c>
-      <c r="O40" s="81" t="s">
+      <c r="O40" s="79" t="s">
         <v>197</v>
       </c>
-      <c r="P40" s="104">
+      <c r="P40" s="102">
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="Q40" s="51">
@@ -4070,7 +4076,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="119"/>
+      <c r="C41" s="127"/>
       <c r="D41" s="45" t="s">
         <v>42</v>
       </c>
@@ -4108,7 +4114,7 @@
       <c r="O41" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="P41" s="89">
+      <c r="P41" s="87">
         <v>1E-3</v>
       </c>
       <c r="Q41" s="54">
@@ -4124,7 +4130,7 @@
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="119"/>
+      <c r="C42" s="127"/>
       <c r="D42" s="41" t="s">
         <v>43</v>
       </c>
@@ -4159,10 +4165,10 @@
       <c r="N42" s="41">
         <v>520</v>
       </c>
-      <c r="O42" s="82" t="s">
+      <c r="O42" s="80" t="s">
         <v>197</v>
       </c>
-      <c r="P42" s="104">
+      <c r="P42" s="102">
         <v>2.46E-2</v>
       </c>
       <c r="Q42" s="51">
@@ -4178,7 +4184,7 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="119"/>
+      <c r="C43" s="127"/>
       <c r="D43" s="45" t="s">
         <v>44</v>
       </c>
@@ -4213,10 +4219,10 @@
       <c r="N43" s="47">
         <v>600</v>
       </c>
-      <c r="O43" s="83" t="s">
+      <c r="O43" s="81" t="s">
         <v>197</v>
       </c>
-      <c r="P43" s="89">
+      <c r="P43" s="87">
         <v>3.3999999999999998E-3</v>
       </c>
       <c r="Q43" s="54">
@@ -4232,7 +4238,7 @@
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="119"/>
+      <c r="C44" s="127"/>
       <c r="D44" s="41" t="s">
         <v>45</v>
       </c>
@@ -4270,7 +4276,7 @@
       <c r="O44" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="P44" s="104">
+      <c r="P44" s="102">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q44" s="51">
@@ -4286,7 +4292,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="120"/>
+      <c r="C45" s="128"/>
       <c r="D45" s="45" t="s">
         <v>46</v>
       </c>
@@ -4321,10 +4327,10 @@
       <c r="N45" s="47">
         <v>1050</v>
       </c>
-      <c r="O45" s="83" t="s">
+      <c r="O45" s="81" t="s">
         <v>197</v>
       </c>
-      <c r="P45" s="89">
+      <c r="P45" s="87">
         <v>1.12E-2</v>
       </c>
       <c r="Q45" s="54">
@@ -4340,7 +4346,7 @@
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="97" t="s">
+      <c r="C46" s="95" t="s">
         <v>114</v>
       </c>
       <c r="D46" s="41" t="s">
@@ -4380,13 +4386,13 @@
       <c r="O46" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="P46" s="105" t="s">
+      <c r="P46" s="103" t="s">
         <v>202</v>
       </c>
       <c r="Q46" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="R46" s="117" t="s">
+      <c r="R46" s="114" t="s">
         <v>231</v>
       </c>
       <c r="S46" s="60" t="s">
@@ -4399,7 +4405,7 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="119" t="s">
+      <c r="C47" s="127" t="s">
         <v>255</v>
       </c>
       <c r="D47" s="45" t="s">
@@ -4437,17 +4443,17 @@
         <v>505</v>
       </c>
       <c r="O47" s="75" t="s">
-        <v>266</v>
-      </c>
-      <c r="P47" s="89">
+        <v>265</v>
+      </c>
+      <c r="P47" s="87">
         <v>2.96</v>
       </c>
       <c r="Q47" s="52">
         <f t="shared" si="2"/>
         <v>1494.8</v>
       </c>
-      <c r="R47" s="114" t="s">
-        <v>267</v>
+      <c r="R47" s="112" t="s">
+        <v>266</v>
       </c>
       <c r="S47" s="49"/>
     </row>
@@ -4457,14 +4463,14 @@
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
-      <c r="C48" s="119"/>
+      <c r="C48" s="127"/>
       <c r="D48" s="41" t="s">
         <v>49</v>
       </c>
       <c r="E48" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="F48" s="100" t="s">
+      <c r="F48" s="98" t="s">
         <v>232</v>
       </c>
       <c r="G48" s="41" t="s">
@@ -4492,10 +4498,10 @@
       <c r="N48" s="41">
         <v>505</v>
       </c>
-      <c r="O48" s="84" t="s">
+      <c r="O48" s="82" t="s">
         <v>197</v>
       </c>
-      <c r="P48" s="104">
+      <c r="P48" s="102">
         <v>3.1503999999999999</v>
       </c>
       <c r="Q48" s="51">
@@ -4511,7 +4517,7 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="120"/>
+      <c r="C49" s="128"/>
       <c r="D49" s="45" t="s">
         <v>50</v>
       </c>
@@ -4543,28 +4549,28 @@
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N49" s="88">
+      <c r="N49" s="86">
         <v>505</v>
       </c>
       <c r="O49" s="75" t="s">
-        <v>266</v>
-      </c>
-      <c r="P49" s="89">
+        <v>265</v>
+      </c>
+      <c r="P49" s="87">
         <v>0.1</v>
       </c>
-      <c r="Q49" s="106">
+      <c r="Q49" s="104">
         <f t="shared" si="2"/>
         <v>50.5</v>
       </c>
-      <c r="R49" s="114" t="s">
-        <v>267</v>
+      <c r="R49" s="112" t="s">
+        <v>266</v>
       </c>
       <c r="S49" s="49"/>
     </row>
     <row r="50" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="31"/>
-      <c r="C50" s="95"/>
+      <c r="C50" s="93"/>
       <c r="D50" s="32" t="s">
         <v>5</v>
       </c>
@@ -4576,45 +4582,45 @@
       <c r="J50" s="34"/>
       <c r="K50" s="35"/>
       <c r="L50" s="35"/>
-      <c r="M50" s="107"/>
-      <c r="N50" s="125" t="s">
+      <c r="M50" s="105"/>
+      <c r="N50" s="119" t="s">
         <v>243</v>
       </c>
-      <c r="O50" s="126"/>
-      <c r="P50" s="126"/>
-      <c r="Q50" s="85">
+      <c r="O50" s="120"/>
+      <c r="P50" s="120"/>
+      <c r="Q50" s="83">
         <f>SUM(Q10:Q49)</f>
-        <v>6190.0655000000006</v>
-      </c>
-      <c r="R50" s="128"/>
-      <c r="S50" s="129"/>
+        <v>6032.228000000001</v>
+      </c>
+      <c r="R50" s="122"/>
+      <c r="S50" s="123"/>
     </row>
     <row r="51" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
-      <c r="B51" s="108"/>
-      <c r="C51" s="109"/>
+      <c r="B51" s="106"/>
+      <c r="C51" s="107"/>
       <c r="D51" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="E51" s="110"/>
-      <c r="F51" s="111"/>
-      <c r="G51" s="112"/>
-      <c r="H51" s="112"/>
-      <c r="I51" s="111"/>
-      <c r="J51" s="111"/>
-      <c r="K51" s="112"/>
-      <c r="L51" s="112"/>
-      <c r="M51" s="113"/>
-      <c r="N51" s="125" t="s">
+      <c r="E51" s="108"/>
+      <c r="F51" s="109"/>
+      <c r="G51" s="110"/>
+      <c r="H51" s="110"/>
+      <c r="I51" s="109"/>
+      <c r="J51" s="109"/>
+      <c r="K51" s="110"/>
+      <c r="L51" s="110"/>
+      <c r="M51" s="111"/>
+      <c r="N51" s="119" t="s">
         <v>245</v>
       </c>
-      <c r="O51" s="126"/>
-      <c r="P51" s="127"/>
-      <c r="Q51" s="87">
-        <v>67.599999999999994</v>
-      </c>
-      <c r="R51" s="130"/>
-      <c r="S51" s="131"/>
+      <c r="O51" s="120"/>
+      <c r="P51" s="121"/>
+      <c r="Q51" s="85">
+        <v>80.599999999999994</v>
+      </c>
+      <c r="R51" s="124"/>
+      <c r="S51" s="125"/>
     </row>
     <row r="52" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
@@ -4628,24 +4634,18 @@
       <c r="K52" s="24"/>
       <c r="L52" s="24"/>
       <c r="M52" s="24"/>
-      <c r="N52" s="125" t="s">
+      <c r="N52" s="119" t="s">
         <v>244</v>
       </c>
-      <c r="O52" s="126"/>
-      <c r="P52" s="126"/>
-      <c r="Q52" s="86">
-        <f>Q50/500</f>
-        <v>12.380131</v>
+      <c r="O52" s="120"/>
+      <c r="P52" s="120"/>
+      <c r="Q52" s="84">
+        <f>SUM(Q50:Q51)/500</f>
+        <v>12.225656000000003</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R50:S51"/>
+  <mergeCells count="19">
     <mergeCell ref="C35:C45"/>
     <mergeCell ref="C47:C49"/>
     <mergeCell ref="C10:C20"/>
@@ -4653,6 +4653,18 @@
     <mergeCell ref="C25:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R50:S51"/>
+    <mergeCell ref="N30:N31"/>
+    <mergeCell ref="O30:O31"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="Q30:Q31"/>
+    <mergeCell ref="S30:S31"/>
+    <mergeCell ref="R30:R31"/>
   </mergeCells>
   <conditionalFormatting sqref="O14">
     <cfRule type="dataBar" priority="15">
@@ -4865,10 +4877,10 @@
     <hyperlink ref="O22" r:id="rId26"/>
     <hyperlink ref="O26" r:id="rId27"/>
     <hyperlink ref="O30" r:id="rId28"/>
-    <hyperlink ref="O31" r:id="rId29"/>
-    <hyperlink ref="O25" r:id="rId30"/>
-    <hyperlink ref="O38" r:id="rId31"/>
-    <hyperlink ref="O36" r:id="rId32"/>
+    <hyperlink ref="O25" r:id="rId29"/>
+    <hyperlink ref="O38" r:id="rId30"/>
+    <hyperlink ref="O36" r:id="rId31"/>
+    <hyperlink ref="O30:O31" r:id="rId32" display="LCSC"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId33"/>

--- a/Deliverables/Interface_Board/BOM/Interface_Board_BOM Quantity(500).xlsx
+++ b/Deliverables/Interface_Board/BOM/Interface_Board_BOM Quantity(500).xlsx
@@ -1703,6 +1703,15 @@
     <xf numFmtId="0" fontId="22" fillId="2" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1739,19 +1748,10 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1819,7 +1819,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2151,15 +2151,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="116"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="119"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2209,7 +2209,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="117"/>
+      <c r="S3" s="120"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2234,7 +2234,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="118"/>
+      <c r="S4" s="121"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2259,7 +2259,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="118"/>
+      <c r="S5" s="121"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2280,7 +2280,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="118"/>
+      <c r="S6" s="121"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2301,7 +2301,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="118"/>
+      <c r="S7" s="121"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2322,7 +2322,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="118"/>
+      <c r="S8" s="121"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2387,7 +2387,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="126" t="s">
+      <c r="C10" s="115" t="s">
         <v>248</v>
       </c>
       <c r="D10" s="41" t="s">
@@ -2443,7 +2443,7 @@
         <f t="shared" ref="B11:B49" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="127"/>
+      <c r="C11" s="116"/>
       <c r="D11" s="45" t="s">
         <v>12</v>
       </c>
@@ -2497,7 +2497,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="127"/>
+      <c r="C12" s="116"/>
       <c r="D12" s="41" t="s">
         <v>13</v>
       </c>
@@ -2551,7 +2551,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="127"/>
+      <c r="C13" s="116"/>
       <c r="D13" s="45" t="s">
         <v>14</v>
       </c>
@@ -2607,7 +2607,7 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="127"/>
+      <c r="C14" s="116"/>
       <c r="D14" s="41" t="s">
         <v>15</v>
       </c>
@@ -2661,7 +2661,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="127"/>
+      <c r="C15" s="116"/>
       <c r="D15" s="45" t="s">
         <v>16</v>
       </c>
@@ -2715,7 +2715,7 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="127"/>
+      <c r="C16" s="116"/>
       <c r="D16" s="41" t="s">
         <v>17</v>
       </c>
@@ -2769,7 +2769,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="127"/>
+      <c r="C17" s="116"/>
       <c r="D17" s="45" t="s">
         <v>18</v>
       </c>
@@ -2823,7 +2823,7 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="127"/>
+      <c r="C18" s="116"/>
       <c r="D18" s="41" t="s">
         <v>19</v>
       </c>
@@ -2877,7 +2877,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="127"/>
+      <c r="C19" s="116"/>
       <c r="D19" s="45" t="s">
         <v>20</v>
       </c>
@@ -2931,7 +2931,7 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="128"/>
+      <c r="C20" s="117"/>
       <c r="D20" s="41" t="s">
         <v>21</v>
       </c>
@@ -2987,7 +2987,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="127" t="s">
+      <c r="C21" s="116" t="s">
         <v>249</v>
       </c>
       <c r="D21" s="45" t="s">
@@ -3043,7 +3043,7 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="127"/>
+      <c r="C22" s="116"/>
       <c r="D22" s="41" t="s">
         <v>23</v>
       </c>
@@ -3097,7 +3097,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="127"/>
+      <c r="C23" s="116"/>
       <c r="D23" s="45" t="s">
         <v>24</v>
       </c>
@@ -3151,7 +3151,7 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="127"/>
+      <c r="C24" s="116"/>
       <c r="D24" s="41" t="s">
         <v>25</v>
       </c>
@@ -3205,7 +3205,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="126" t="s">
+      <c r="C25" s="115" t="s">
         <v>250</v>
       </c>
       <c r="D25" s="45" t="s">
@@ -3263,7 +3263,7 @@
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="127"/>
+      <c r="C26" s="116"/>
       <c r="D26" s="41" t="s">
         <v>27</v>
       </c>
@@ -3317,7 +3317,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="128"/>
+      <c r="C27" s="117"/>
       <c r="D27" s="45" t="s">
         <v>28</v>
       </c>
@@ -3366,7 +3366,7 @@
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="126" t="s">
+      <c r="C28" s="115" t="s">
         <v>251</v>
       </c>
       <c r="D28" s="41" t="s">
@@ -3422,7 +3422,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="128"/>
+      <c r="C29" s="117"/>
       <c r="D29" s="45" t="s">
         <v>30</v>
       </c>
@@ -3478,7 +3478,7 @@
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="126" t="s">
+      <c r="C30" s="115" t="s">
         <v>250</v>
       </c>
       <c r="D30" s="41" t="s">
@@ -3512,7 +3512,7 @@
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N30" s="130">
+      <c r="N30" s="129">
         <v>500</v>
       </c>
       <c r="O30" s="131" t="s">
@@ -3525,7 +3525,7 @@
         <f>P30*N30</f>
         <v>44.2</v>
       </c>
-      <c r="R30" s="130"/>
+      <c r="R30" s="129"/>
       <c r="S30" s="136" t="s">
         <v>268</v>
       </c>
@@ -3536,7 +3536,7 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="127"/>
+      <c r="C31" s="116"/>
       <c r="D31" s="45" t="s">
         <v>32</v>
       </c>
@@ -3568,11 +3568,11 @@
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N31" s="129"/>
+      <c r="N31" s="130"/>
       <c r="O31" s="132"/>
       <c r="P31" s="134"/>
       <c r="Q31" s="134"/>
-      <c r="R31" s="129"/>
+      <c r="R31" s="130"/>
       <c r="S31" s="137"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3750,7 +3750,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="126" t="s">
+      <c r="C35" s="115" t="s">
         <v>254</v>
       </c>
       <c r="D35" s="45" t="s">
@@ -3806,7 +3806,7 @@
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="127"/>
+      <c r="C36" s="116"/>
       <c r="D36" s="41" t="s">
         <v>37</v>
       </c>
@@ -3860,7 +3860,7 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="127"/>
+      <c r="C37" s="116"/>
       <c r="D37" s="45" t="s">
         <v>38</v>
       </c>
@@ -3914,7 +3914,7 @@
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="127"/>
+      <c r="C38" s="116"/>
       <c r="D38" s="41" t="s">
         <v>39</v>
       </c>
@@ -3968,7 +3968,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="127"/>
+      <c r="C39" s="116"/>
       <c r="D39" s="45" t="s">
         <v>40</v>
       </c>
@@ -4022,7 +4022,7 @@
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="127"/>
+      <c r="C40" s="116"/>
       <c r="D40" s="41" t="s">
         <v>41</v>
       </c>
@@ -4076,7 +4076,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="127"/>
+      <c r="C41" s="116"/>
       <c r="D41" s="45" t="s">
         <v>42</v>
       </c>
@@ -4130,7 +4130,7 @@
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="127"/>
+      <c r="C42" s="116"/>
       <c r="D42" s="41" t="s">
         <v>43</v>
       </c>
@@ -4184,7 +4184,7 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="127"/>
+      <c r="C43" s="116"/>
       <c r="D43" s="45" t="s">
         <v>44</v>
       </c>
@@ -4238,7 +4238,7 @@
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="127"/>
+      <c r="C44" s="116"/>
       <c r="D44" s="41" t="s">
         <v>45</v>
       </c>
@@ -4292,7 +4292,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="128"/>
+      <c r="C45" s="117"/>
       <c r="D45" s="45" t="s">
         <v>46</v>
       </c>
@@ -4405,7 +4405,7 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="127" t="s">
+      <c r="C47" s="116" t="s">
         <v>255</v>
       </c>
       <c r="D47" s="45" t="s">
@@ -4463,7 +4463,7 @@
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
-      <c r="C48" s="127"/>
+      <c r="C48" s="116"/>
       <c r="D48" s="41" t="s">
         <v>49</v>
       </c>
@@ -4517,7 +4517,7 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="128"/>
+      <c r="C49" s="117"/>
       <c r="D49" s="45" t="s">
         <v>50</v>
       </c>
@@ -4583,17 +4583,17 @@
       <c r="K50" s="35"/>
       <c r="L50" s="35"/>
       <c r="M50" s="105"/>
-      <c r="N50" s="119" t="s">
+      <c r="N50" s="122" t="s">
         <v>243</v>
       </c>
-      <c r="O50" s="120"/>
-      <c r="P50" s="120"/>
+      <c r="O50" s="123"/>
+      <c r="P50" s="123"/>
       <c r="Q50" s="83">
         <f>SUM(Q10:Q49)</f>
         <v>6032.228000000001</v>
       </c>
-      <c r="R50" s="122"/>
-      <c r="S50" s="123"/>
+      <c r="R50" s="125"/>
+      <c r="S50" s="126"/>
     </row>
     <row r="51" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
@@ -4611,16 +4611,16 @@
       <c r="K51" s="110"/>
       <c r="L51" s="110"/>
       <c r="M51" s="111"/>
-      <c r="N51" s="119" t="s">
+      <c r="N51" s="122" t="s">
         <v>245</v>
       </c>
-      <c r="O51" s="120"/>
-      <c r="P51" s="121"/>
+      <c r="O51" s="123"/>
+      <c r="P51" s="124"/>
       <c r="Q51" s="85">
         <v>80.599999999999994</v>
       </c>
-      <c r="R51" s="124"/>
-      <c r="S51" s="125"/>
+      <c r="R51" s="127"/>
+      <c r="S51" s="128"/>
     </row>
     <row r="52" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
@@ -4634,11 +4634,11 @@
       <c r="K52" s="24"/>
       <c r="L52" s="24"/>
       <c r="M52" s="24"/>
-      <c r="N52" s="119" t="s">
+      <c r="N52" s="122" t="s">
         <v>244</v>
       </c>
-      <c r="O52" s="120"/>
-      <c r="P52" s="120"/>
+      <c r="O52" s="123"/>
+      <c r="P52" s="123"/>
       <c r="Q52" s="84">
         <f>SUM(Q50:Q51)/500</f>
         <v>12.225656000000003</v>
@@ -4646,13 +4646,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C35:C45"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="C10:C20"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="C30:C31"/>
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
     <mergeCell ref="N50:P50"/>
@@ -4665,6 +4658,13 @@
     <mergeCell ref="Q30:Q31"/>
     <mergeCell ref="S30:S31"/>
     <mergeCell ref="R30:R31"/>
+    <mergeCell ref="C35:C45"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="C10:C20"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="C30:C31"/>
   </mergeCells>
   <conditionalFormatting sqref="O14">
     <cfRule type="dataBar" priority="15">
